--- a/news_daily/2026-10-22.xlsx
+++ b/news_daily/2026-10-22.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -987,6 +1011,10 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1189,6 +1217,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1399,6 +1431,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1557,6 +1593,10 @@
       <c r="BF5" s="2" t="inlineStr"/>
       <c r="BG5" s="2" t="inlineStr"/>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1751,6 +1791,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1973,6 +2017,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2195,6 +2243,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2389,6 +2441,10 @@
       <c r="BF9" s="3" t="inlineStr"/>
       <c r="BG9" s="3" t="inlineStr"/>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2547,6 +2603,10 @@
       <c r="BF10" s="2" t="inlineStr"/>
       <c r="BG10" s="2" t="inlineStr"/>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2753,6 +2813,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2971,6 +3035,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3021,17 +3089,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr"/>
@@ -3072,7 +3140,11 @@
       </c>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>26a18dcdf2284982ab66c202c8cc9615</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>fff03a0fd409bebaa971460f</t>
@@ -3131,7 +3203,7 @@
       </c>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP13" s="4" t="inlineStr">
@@ -3173,6 +3245,18 @@
       <c r="BF13" s="4" t="inlineStr"/>
       <c r="BG13" s="4" t="inlineStr"/>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3227,17 +3311,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr"/>
@@ -3278,7 +3362,11 @@
       </c>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>72f7e40ac43f43e3aff08819995be98f</t>
+        </is>
+      </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>b921d8e12af42c124b1a45c8</t>
@@ -3329,7 +3417,7 @@
       </c>
       <c r="AO14" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP14" s="4" t="inlineStr">
@@ -3391,9 +3479,21 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH14"/>
+  <autoFilter ref="A1:BL14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3404,7 +3504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3467,6 +3567,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3768,6 +3872,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3992,6 +4116,10 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4214,6 +4342,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4408,6 +4540,10 @@
       <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="inlineStr"/>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4458,17 +4594,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
@@ -4509,7 +4645,11 @@
       </c>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>26a18dcdf2284982ab66c202c8cc9615</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>fff03a0fd409bebaa971460f</t>
@@ -4568,7 +4708,7 @@
       </c>
       <c r="AO5" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" s="4" t="inlineStr">
@@ -4610,6 +4750,18 @@
       <c r="BF5" s="4" t="inlineStr"/>
       <c r="BG5" s="4" t="inlineStr"/>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4664,17 +4816,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr"/>
@@ -4715,7 +4867,11 @@
       </c>
       <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>72f7e40ac43f43e3aff08819995be98f</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>b921d8e12af42c124b1a45c8</t>
@@ -4766,7 +4922,7 @@
       </c>
       <c r="AO6" s="4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" s="4" t="inlineStr">
@@ -4828,9 +4984,21 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4841,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4904,6 +5072,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5205,6 +5377,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5557,10 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5567,6 +5763,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5777,6 +5977,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5935,6 +6139,10 @@
       <c r="BF5" s="2" t="inlineStr"/>
       <c r="BG5" s="2" t="inlineStr"/>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6129,6 +6337,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -6351,6 +6563,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -6545,6 +6761,10 @@
       <c r="BF8" s="3" t="inlineStr"/>
       <c r="BG8" s="3" t="inlineStr"/>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6703,6 +6923,10 @@
       <c r="BF9" s="2" t="inlineStr"/>
       <c r="BG9" s="2" t="inlineStr"/>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6909,429 +7133,13 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RNDC</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T04:14:22+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>RNDC 申請第 11 章破產，並計畫出售資產及逐步關閉營運。</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>RNDC</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPaXkxbTd3WFRlMnNJQ1F0akZGS1BnYkR4bHBtODR6Ynhqb2hUWXVxNkdMVzNUUFJxNzJZMHdOR3MyQU5BMmptb3VDQ005ME40cHRRR3FkQXVtcTJkcl8yY3owRV9ZeWdCazBOVEh6SzVXX2lrOVRBMXQ5T09Qc3ljWldyUkVEZ1V5YkNZ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>National Association of Wholesaler-Distributors</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>fff03a0fd409bebaa971460f</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>5a0e0d95455677066de7d303</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RNDC Files for Chapter 11, Pursues Sales and Wind-Down &amp;nbsp;&amp;nbsp; National Association of Wholesaler-Distributors </t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr">
-        <is>
-          <t>chapter 11</t>
-        </is>
-      </c>
-      <c r="AJ11" s="4" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="AK11" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL11" s="4" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AM11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN11" s="4" t="inlineStr">
-        <is>
-          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
-        </is>
-      </c>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ11" s="4" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR11" s="4" t="inlineStr">
-        <is>
-          <t>1470</t>
-        </is>
-      </c>
-      <c r="AS11" s="4" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr"/>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr"/>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>EONR</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>EON Resources Inc. Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T03:47:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Eon Resources 公司的 CEO 在面臨持續的營運疑慮警告時，表示公司仍具足夠流動性以維持營運。</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>繼續經營疑慮</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>GOING_CONCERN|LIQUIDITY_CRISIS</t>
-        </is>
-      </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>Eon Resources</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNX0hvNGdTa0Vzakk2Sndrb0xlaFJzQWtVNzM5SHpTeWpjYUY2Y0FDdFljNkk5UllGakdhaWFSbXJfTTJTMmQzQl9Mc3ZhcGFyemphUmx0NFMyekcxVXlkX3Z2MXJXQldaRFpnT3JSNHhqc2Y5NThTM2NBTGdNMmVTNVRqREgyQVpxUEVON0FjdjNFS3k5UVhYdnN3?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Hart Energy</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>GOING_CONCERN</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>b921d8e12af42c124b1a45c8</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>a18bd00bf42db9315918f062</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings &amp;nbsp;&amp;nbsp; Hart Energy </t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL12" s="4" t="inlineStr">
-        <is>
-          <t>RUMORED</t>
-        </is>
-      </c>
-      <c r="AM12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN12" s="4" t="inlineStr">
-        <is>
-          <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
-        </is>
-      </c>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ12" s="4" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR12" s="4" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-      <c r="AS12" s="4" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE American</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>EONR</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH12"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7342,7 +7150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7405,6 +7213,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7708,9 +7520,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7721,7 +7553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7771,134 +7603,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7908,46 +7740,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7956,12 +7822,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7971,90 +7837,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -8064,94 +7934,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -8159,89 +8029,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-22.xlsx
+++ b/news_daily/2026-10-22.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -96,6 +101,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -882,20 +890,36 @@
           <t>無足夠資訊確認任何信用風險事件。</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -919,10 +943,18 @@
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>4b8711028e2f4858abd70d0c97c55756</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>5a3dcc8b183e83f67a3ad671</t>
@@ -969,7 +1001,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr">
@@ -1011,10 +1043,22 @@
       <c r="BF2" s="2" t="inlineStr"/>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1052,20 +1096,36 @@
           <t>Meta 相關訊息未顯示任何確定的違約或信用事件，僅提及市場股價波動，無法判斷是否存在信用風險升高或違約情形。</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>股價下跌</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -1093,10 +1153,18 @@
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>PRICE_MOVEMENT</t>
+        </is>
+      </c>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>430bb059e12743fdb48d6885c465dc81</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>804abe3a8136f62a9c1c950c</t>
@@ -1151,7 +1219,7 @@
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="2" t="inlineStr">
@@ -1217,10 +1285,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1275,15 +1355,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -1322,7 +1406,11 @@
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>0da4ee9e699d4bb295095137c65a0dda</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>c75869506577c88d3a17781a</t>
@@ -1369,7 +1457,7 @@
       <c r="AN4" s="2" t="inlineStr"/>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP4" s="2" t="inlineStr">
@@ -1433,8 +1521,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1464,20 +1560,36 @@
           <t>無足夠資訊確認任何信用風險事件。</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -1501,10 +1613,18 @@
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>3e4f9bb0e52c46e499ca47d408d28ff6</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>50b863c0289f5cb1cca8cdd4</t>
@@ -1551,7 +1671,7 @@
       <c r="AN5" s="2" t="inlineStr"/>
       <c r="AO5" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" s="2" t="inlineStr">
@@ -1593,858 +1713,954 @@
       <c r="BF5" s="2" t="inlineStr"/>
       <c r="BG5" s="2" t="inlineStr"/>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>PZZA</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Papa John's International, Inc.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-10-22T22:03:27+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>本新聞未提供足夠證據顯示 Papa John's International, Inc. 有任何違約、破產或其他信用風險事件，僅提及投資者可領導訴訟。</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>Papa John's International, Inc.</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxPM1I4Ujg5QzFMbVpvQWV0enFIVEtMVTdCd2N4eWp4ZUw1NXRRUkF4cDRsR0FHd0hhcnQzVnpXZTdnd2FYaW9FbV81SF9VNG51ZzJLRnVYNWY5azdtN0JlNXgybkpKaGViaW56MHhkd2R3YTc2ZV9DWlJ6YVdaOUhTOG1CNU5CNEJTM0I3WERiM0tDVFVXZFpkWnFFb3JXV3gzc250Q2hyVkFMb2NzVnJKQW5BMkFPeVVKLU1aaWpabFJ6YzV0UmdoclB6d0xSVHl6bEptN2EyQ29BV0FNaVl4RkljTHp4Z1EtanlORzBJd0c3V0Fvc1RQcEg4UGpQMEtLSW92ZGhQX0o0M2otbnRaMW5NeHZEb2dfeTZfOTNBVXhBazM1RE5rNmVVYk1ZMGw5c0pEaWVJekc?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>The Daily Tribune News</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>f19cc8b1b02f42ddb176a28c87ddc756</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>9a99478b2900cd4f54743ca2</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>7f0886ef1cbe99fa784a57ba</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>MARKET_DISCOVERY</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law &amp;nbsp;&amp;nbsp; The Daily Tribune News </t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>Papa John's International, Inc.</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxPM1I4Ujg5QzFMbVpvQWV0enFIVEtMVTdCd2N4eWp4ZUw1NXRRUkF4cDRsR0FHd0hhcnQzVnpXZTdnd2FYaW9FbV81SF9VNG51ZzJLRnVYNWY5azdtN0JlNXgybkpKaGViaW56MHhkd2R3YTc2ZV9DWlJ6YVdaOUhTOG1CNU5CNEJTM0I3WERiM0tDVFVXZFpkWnFFb3JXV3gzc250Q2hyVkFMb2NzVnJKQW5BMkFPeVVKLU1aaWpabFJ6YzV0UmdoclB6d0xSVHl6bEptN2EyQ29BV0FNaVl4RkljTHp4Z1EtanlORzBJd0c3V0Fvc1RQcEg4UGpQMEtLSW92ZGhQX0o0M2otbnRaMW5NeHZEb2dfeTZfOTNBVXhBazM1RE5rNmVVYk1ZMGw5c0pEaWVJekc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>The Daily Tribune News</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>9a99478b2900cd4f54743ca2</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>7f0886ef1cbe99fa784a57ba</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law &amp;nbsp;&amp;nbsp; The Daily Tribune News </t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ6" s="2" t="inlineStr">
+      <c r="AQ6" s="3" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR6" s="2" t="inlineStr">
+      <c r="AR6" s="3" t="inlineStr">
         <is>
           <t>1477</t>
         </is>
       </c>
-      <c r="AS6" s="2" t="inlineStr">
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>PZZA</t>
         </is>
       </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>PHM</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>PulteGroup, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-10-22T20:22:46+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE)</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>普爾特集團因第三季財報未達預期，股價下跌，顯示市場對住宅需求的擔憂。</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>財報不如預期</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>已分類</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>PulteGroup</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYm53VTh3QTFRckszZ25LR1dydXhWTlVXejhia2pMcjFkVl9XOFNteERCSmNLNGNXTDZ5aUwycjRaMWV3emdQYmtJdThObWVVNE9mNlBOQWxXcUZUdWdMQlBxYmtRWFFxa0lrZmpETkVPQ2tGUlh1dER2Rk5MR1AyR3ByVTlmajlpV1ItN3BVbDgyRjVxOFFORXdLT1VkUDVKRlp1VFEtd2NNZ0hTd0Vfdng2TTdkQ0ozUHZVcjY4SjYxdw?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="3" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>c9b4b17dbf714cbcbbfcf5cb80d7eeab</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>121df6b8d1583e63199ddab7</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="inlineStr">
+      <c r="AD7" s="4" t="inlineStr">
         <is>
           <t>a2ffa540ad4cc1c9e2785913</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG7" s="3" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE) &amp;nbsp;&amp;nbsp; Seeking Alpha </t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI7" s="3" t="inlineStr">
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>earnings miss</t>
         </is>
       </c>
-      <c r="AJ7" s="3" t="inlineStr">
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="AK7" s="3" t="inlineStr">
+      <c r="AK7" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL7" s="3" t="inlineStr">
+      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
+      <c r="AM7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
+      <c r="AN7" s="4" t="inlineStr">
         <is>
           <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand</t>
         </is>
       </c>
-      <c r="AO7" s="3" t="inlineStr">
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ7" s="3" t="inlineStr">
+      <c r="AQ7" s="4" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR7" s="3" t="inlineStr">
+      <c r="AR7" s="4" t="inlineStr">
         <is>
           <t>1487</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AS7" s="4" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
         <is>
           <t>PHM</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-10-22T20:04:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>IBM 受七月營收不及預期影響，股價下跌，市場對其財務表現表現出擔憂。</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>財報不如預期</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNN1g2QmJPSjM4RGNlSFFkSmxheU0wQnp5UkVWSlpRU3drc05lMG1oQmZrRVZUbnlaaUNGVlBfd1ZSQ0V4YkhnYVh6dmNJVnZIUXRPek5VRlVfZDZocGNfTVRzZkNpMjhsWXhvNVdrNXo1UjRDbC1lZlVrRnM2TG03M280R3E3SWF0SzhBVHNPZGx6aVdzRnlRTEtYem9CT0hRWnREVDBPLVg3ZzgyRjBnc3B1OA?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>MarketWatch</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>625beff756514b18baea6459f9318ed9</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>4df070360f41de2f4d8ffca0</t>
         </is>
       </c>
-      <c r="AD8" s="3" t="inlineStr">
+      <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>15814b5497b98f167c845463</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG8" s="3" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> IBM’s stock falls as investors struggle to shake off July earnings miss &amp;nbsp;&amp;nbsp; MarketWatch </t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>earnings miss</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="AK8" s="3" t="inlineStr">
+      <c r="AK8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL8" s="3" t="inlineStr">
+      <c r="AL8" s="4" t="inlineStr">
         <is>
           <t>MARKET_IMPLIED</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
+      <c r="AM8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
+      <c r="AN8" s="4" t="inlineStr">
         <is>
           <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
         </is>
       </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP8" s="4" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ8" s="3" t="inlineStr">
+      <c r="AQ8" s="4" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR8" s="3" t="inlineStr">
+      <c r="AR8" s="4" t="inlineStr">
         <is>
           <t>1459</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AS8" s="4" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Kenyan Company</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T16:32:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Kenyan Company Issues Fifth Profit Warning In Five Years</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>肯尼亞公司在五年內第五次發布利潤警告，顯示其財務表現不佳。</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>EARNINGS_WARNING</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>Kenyan Company</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>公司代號待核對</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUUJQQUVhaXJra3ZCVXVpdU5UT3JWU0lhOU5ETG9rbjJPM1RUbVBheE4teWZSRFJmRkU5N3dnWFlaZjdjSjJNSjAyTVhMcHZjUTdjSEZadmlnUkRvODd0TlJhVzFNYTRBX2Z2MnZXSFk2Sy1ZUDJoamg2SmpkVTFOMmRiVElPWThSb1ZEcG0tTGpMNDVQUS1j?oc=5</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>The Kenya Times</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>d43f527802444a9a8ae0d7a5105689a6</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>a6d594bd8815899279a12f3d</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>ae9ecbb34a3046b47d87afd5</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>MARKET_DISCOVERY</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Kenyan Company Issues Fifth Profit Warning In Five Years &amp;nbsp;&amp;nbsp; The Kenya Times </t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>profit warning</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
         <is>
           <t>EARNINGS_WARNING</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr"/>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>a6d594bd8815899279a12f3d</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>ae9ecbb34a3046b47d87afd5</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Kenyan Company Issues Fifth Profit Warning In Five Years &amp;nbsp;&amp;nbsp; The Kenya Times </t>
-        </is>
-      </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI9" s="3" t="inlineStr">
-        <is>
-          <t>profit warning</t>
-        </is>
-      </c>
-      <c r="AJ9" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
+      <c r="AK9" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL9" s="3" t="inlineStr">
+      <c r="AL9" s="2" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
+      <c r="AM9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP9" s="2" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ9" s="3" t="inlineStr">
+      <c r="AQ9" s="2" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR9" s="3" t="inlineStr">
+      <c r="AR9" s="2" t="inlineStr">
         <is>
           <t>1453</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AS9" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr"/>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr"/>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>公司代號待核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr"/>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr"/>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr"/>
+      <c r="BF9" s="2" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2474,20 +2690,36 @@
           <t>無可辨識的信用風險事件。</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -2511,10 +2743,18 @@
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>d0373f9eac4d42319fc8032494a30ee4</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>fbff431e27558bb00d62e9a4</t>
@@ -2561,7 +2801,7 @@
       <c r="AN10" s="2" t="inlineStr"/>
       <c r="AO10" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" s="2" t="inlineStr">
@@ -2603,220 +2843,256 @@
       <c r="BF10" s="2" t="inlineStr"/>
       <c r="BG10" s="2" t="inlineStr"/>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-10-22T07:23:22+08:00</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Abbott to spin out Nutrition business, cuts guidance</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>阿博特公司將其營養業務拆分，並下調指引，屬於一般公司更新。</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>一般公司更新</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>排除、不納入風險事件</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>財測下修</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>GENERAL_INFORMATION</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPVlY1aFVobmxHUG9RUGJ3UFdvSk44SzJNS3J6Ni1ZemEzTlY3LUFsdTVIc0ZCaENHX09VWUVIeThlMTQ4TkVYdUhyVUpHNmZfUXByR3BQSWk4YzRTTzRXS1BndGRGS2ZKS29Ebkoxb2tiZjlPZmx3cWFaaUd5QUJWRlIwTFVYdw?oc=5</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>MassDevice</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL_INFORMATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>EARNINGS_WARNING</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr"/>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>7898337efd704d62ae39dbe64c320590</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>9cd60119472fd0edfd22e915</t>
         </is>
       </c>
-      <c r="AD11" s="2" t="inlineStr">
+      <c r="AD11" s="4" t="inlineStr">
         <is>
           <t>8a85ef4535a887fa86a24eab</t>
         </is>
       </c>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG11" s="2" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> Abbott to spin out Nutrition business, cuts guidance &amp;nbsp;&amp;nbsp; MassDevice </t>
         </is>
       </c>
-      <c r="AH11" s="2" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr">
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL11" s="2" t="inlineStr">
+      <c r="AL11" s="4" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="AM11" s="2" t="inlineStr">
+      <c r="AM11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="2" t="inlineStr">
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP11" s="4" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ11" s="2" t="inlineStr">
+      <c r="AQ11" s="4" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR11" s="2" t="inlineStr">
+      <c r="AR11" s="4" t="inlineStr">
         <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="AS11" s="2" t="inlineStr">
+      <c r="AS11" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="BC11" s="2" t="inlineStr">
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="2" t="inlineStr"/>
-      <c r="BE11" s="2" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
-      <c r="BF11" s="2" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG11" s="2" t="inlineStr">
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
-      <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,452 +3317,452 @@
       <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>RNDC</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2026-10-22T04:14:22+08:00</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>RNDC 申請第 11 章破產，並計畫出售資產及逐步關閉營運。</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>破產</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>BANKRUPTCY</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>RNDC</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>公司代號待核對</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPaXkxbTd3WFRlMnNJQ1F0akZGS1BnYkR4bHBtODR6Ynhqb2hUWXVxNkdMVzNUUFJxNzJZMHdOR3MyQU5BMmptb3VDQ005ME40cHRRR3FkQXVtcTJkcl8yY3owRV9ZeWdCazBOVEh6SzVXX2lrOVRBMXQ5T09Qc3ljWldyUkVEZ1V5YkNZ?oc=5</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>National Association of Wholesaler-Distributors</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr">
         <is>
           <t>BANKRUPTCY</t>
         </is>
       </c>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="AA13" s="5" t="inlineStr"/>
+      <c r="AB13" s="5" t="inlineStr">
         <is>
           <t>26a18dcdf2284982ab66c202c8cc9615</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AC13" s="5" t="inlineStr">
         <is>
           <t>fff03a0fd409bebaa971460f</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AD13" s="5" t="inlineStr">
         <is>
           <t>5a0e0d95455677066de7d303</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AE13" s="5" t="inlineStr"/>
+      <c r="AF13" s="5" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AG13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> RNDC Files for Chapter 11, Pursues Sales and Wind-Down &amp;nbsp;&amp;nbsp; National Association of Wholesaler-Distributors </t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
+      <c r="AH13" s="5" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI13" s="4" t="inlineStr">
+      <c r="AI13" s="5" t="inlineStr">
         <is>
           <t>chapter 11</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr">
+      <c r="AJ13" s="5" t="inlineStr">
         <is>
           <t>BANKRUPTCY</t>
         </is>
       </c>
-      <c r="AK13" s="4" t="inlineStr">
+      <c r="AK13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL13" s="4" t="inlineStr">
+      <c r="AL13" s="5" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="AM13" s="4" t="inlineStr">
+      <c r="AM13" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN13" s="4" t="inlineStr">
+      <c r="AN13" s="5" t="inlineStr">
         <is>
           <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
         </is>
       </c>
-      <c r="AO13" s="4" t="inlineStr">
+      <c r="AO13" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP13" s="4" t="inlineStr">
+      <c r="AP13" s="5" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ13" s="4" t="inlineStr">
+      <c r="AQ13" s="5" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR13" s="4" t="inlineStr">
+      <c r="AR13" s="5" t="inlineStr">
         <is>
           <t>1470</t>
         </is>
       </c>
-      <c r="AS13" s="4" t="inlineStr">
+      <c r="AS13" s="5" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr"/>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="AT13" s="5" t="inlineStr"/>
+      <c r="AU13" s="5" t="inlineStr"/>
+      <c r="AV13" s="5" t="inlineStr"/>
+      <c r="AW13" s="5" t="inlineStr"/>
+      <c r="AX13" s="5" t="inlineStr"/>
+      <c r="AY13" s="5" t="inlineStr"/>
+      <c r="AZ13" s="5" t="inlineStr"/>
+      <c r="BA13" s="5" t="inlineStr"/>
+      <c r="BB13" s="5" t="inlineStr"/>
+      <c r="BC13" s="5" t="inlineStr">
         <is>
           <t>公司代號待核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr"/>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr"/>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr">
+      <c r="BD13" s="5" t="inlineStr"/>
+      <c r="BE13" s="5" t="inlineStr"/>
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr"/>
+      <c r="BI13" s="5" t="inlineStr"/>
+      <c r="BJ13" s="5" t="inlineStr"/>
+      <c r="BK13" s="5" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL13" s="4" t="inlineStr">
+      <c r="BL13" s="5" t="inlineStr">
         <is>
           <t>2026-10-26T15:43:17.016263+08:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>EONR</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>EON Resources Inc. Class A Common Stock</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>2026-10-22T03:47:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Eon Resources 公司的 CEO 在面臨持續的營運疑慮警告時，表示公司仍具足夠流動性以維持營運。</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>繼續經營疑慮</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>GOING_CONCERN|LIQUIDITY_CRISIS</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>Eon Resources</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNX0hvNGdTa0Vzakk2Sndrb0xlaFJzQWtVNzM5SHpTeWpjYUY2Y0FDdFljNkk5UllGakdhaWFSbXJfTTJTMmQzQl9Mc3ZhcGFyemphUmx0NFMyekcxVXlkX3Z2MXJXQldaRFpnT3JSNHhqc2Y5NThTM2NBTGdNMmVTNVRqREgyQVpxUEVON0FjdjNFS3k5UVhYdnN3?oc=5</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>Hart Energy</t>
         </is>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr">
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr">
         <is>
           <t>GOING_CONCERN</t>
         </is>
       </c>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr">
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="5" t="inlineStr"/>
+      <c r="AB14" s="5" t="inlineStr">
         <is>
           <t>72f7e40ac43f43e3aff08819995be98f</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AC14" s="5" t="inlineStr">
         <is>
           <t>b921d8e12af42c124b1a45c8</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AD14" s="5" t="inlineStr">
         <is>
           <t>a18bd00bf42db9315918f062</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AE14" s="5" t="inlineStr"/>
+      <c r="AF14" s="5" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AG14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings &amp;nbsp;&amp;nbsp; Hart Energy </t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
+      <c r="AH14" s="5" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr">
+      <c r="AI14" s="5" t="inlineStr"/>
+      <c r="AJ14" s="5" t="inlineStr"/>
+      <c r="AK14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL14" s="4" t="inlineStr">
+      <c r="AL14" s="5" t="inlineStr">
         <is>
           <t>RUMORED</t>
         </is>
       </c>
-      <c r="AM14" s="4" t="inlineStr">
+      <c r="AM14" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN14" s="4" t="inlineStr">
+      <c r="AN14" s="5" t="inlineStr">
         <is>
           <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
         </is>
       </c>
-      <c r="AO14" s="4" t="inlineStr">
+      <c r="AO14" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP14" s="4" t="inlineStr">
+      <c r="AP14" s="5" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ14" s="4" t="inlineStr">
+      <c r="AQ14" s="5" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR14" s="4" t="inlineStr">
+      <c r="AR14" s="5" t="inlineStr">
         <is>
           <t>1465</t>
         </is>
       </c>
-      <c r="AS14" s="4" t="inlineStr">
+      <c r="AS14" s="5" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
+      <c r="AT14" s="5" t="inlineStr"/>
+      <c r="AU14" s="5" t="inlineStr"/>
+      <c r="AV14" s="5" t="inlineStr"/>
+      <c r="AW14" s="5" t="inlineStr">
         <is>
           <t>NYSE American</t>
         </is>
       </c>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
+      <c r="AX14" s="5" t="inlineStr"/>
+      <c r="AY14" s="5" t="inlineStr"/>
+      <c r="AZ14" s="5" t="inlineStr"/>
+      <c r="BA14" s="5" t="inlineStr"/>
+      <c r="BB14" s="5" t="inlineStr">
         <is>
           <t>EONR</t>
         </is>
       </c>
-      <c r="BC14" s="4" t="inlineStr">
+      <c r="BC14" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
+      <c r="BD14" s="5" t="inlineStr"/>
+      <c r="BE14" s="5" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="4" t="inlineStr">
+      <c r="BF14" s="5" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="4" t="inlineStr">
+      <c r="BG14" s="5" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr">
+      <c r="BH14" s="5" t="inlineStr"/>
+      <c r="BI14" s="5" t="inlineStr"/>
+      <c r="BJ14" s="5" t="inlineStr"/>
+      <c r="BK14" s="5" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL14" s="4" t="inlineStr">
+      <c r="BL14" s="5" t="inlineStr">
         <is>
           <t>2026-10-26T15:43:17.016263+08:00</t>
         </is>
@@ -3504,7 +3780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3908,67 +4184,67 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>PZZA</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>PulteGroup, Inc. Common Stock</t>
+          <t>Papa John's International, Inc.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22T20:22:46+08:00</t>
+          <t>2026-10-22T22:03:27+08:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE)</t>
+          <t>PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>普爾特集團因第三季財報未達預期，股價下跌，顯示市場對住宅需求的擔憂。</t>
+          <t>本新聞未提供足夠證據顯示 Papa John's International, Inc. 有任何違約、破產或其他信用風險事件，僅提及投資者可領導訴訟。</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>已分類</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="N2" s="3" t="inlineStr"/>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
-        </is>
-      </c>
+      <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>Papa John's International, Inc.</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -3978,32 +4254,36 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYm53VTh3QTFRckszZ25LR1dydXhWTlVXejhia2pMcjFkVl9XOFNteERCSmNLNGNXTDZ5aUwycjRaMWV3emdQYmtJdThObWVVNE9mNlBOQWxXcUZUdWdMQlBxYmtRWFFxa0lrZmpETkVPQ2tGUlh1dER2Rk5MR1AyR3ByVTlmajlpV1ItN3BVbDgyRjVxOFFORXdLT1VkUDVKRlp1VFEtd2NNZ0hTd0Vfdng2TTdkQ0ozUHZVcjY4SjYxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxPM1I4Ujg5QzFMbVpvQWV0enFIVEtMVTdCd2N4eWp4ZUw1NXRRUkF4cDRsR0FHd0hhcnQzVnpXZTdnd2FYaW9FbV81SF9VNG51ZzJLRnVYNWY5azdtN0JlNXgybkpKaGViaW56MHhkd2R3YTc2ZV9DWlJ6YVdaOUhTOG1CNU5CNEJTM0I3WERiM0tDVFVXZFpkWnFFb3JXV3gzc250Q2hyVkFMb2NzVnJKQW5BMkFPeVVKLU1aaWpabFJ6YzV0UmdoclB6d0xSVHl6bEptN2EyQ29BV0FNaVl4RkljTHp4Z1EtanlORzBJd0c3V0Fvc1RQcEg4UGpQMEtLSW92ZGhQX0o0M2otbnRaMW5NeHZEb2dfeTZfOTNBVXhBazM1RE5rNmVVYk1ZMGw5c0pEaWVJekc?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>The Daily Tribune News</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr"/>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>f19cc8b1b02f42ddb176a28c87ddc756</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>121df6b8d1583e63199ddab7</t>
+          <t>9a99478b2900cd4f54743ca2</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>a2ffa540ad4cc1c9e2785913</t>
+          <t>7f0886ef1cbe99fa784a57ba</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -4014,7 +4294,7 @@
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE) &amp;nbsp;&amp;nbsp; Seeking Alpha </t>
+          <t xml:space="preserve"> PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law &amp;nbsp;&amp;nbsp; The Daily Tribune News </t>
         </is>
       </c>
       <c r="AH2" s="3" t="inlineStr">
@@ -4022,16 +4302,8 @@
           <t>en</t>
         </is>
       </c>
-      <c r="AI2" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AJ2" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
       <c r="AK2" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4039,7 +4311,7 @@
       </c>
       <c r="AL2" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>UNCLEAR</t>
         </is>
       </c>
       <c r="AM2" s="3" t="inlineStr">
@@ -4047,11 +4319,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand</t>
-        </is>
-      </c>
+      <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
@@ -4069,12 +4337,12 @@
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AT2" s="3" t="inlineStr"/>
@@ -4082,7 +4350,7 @@
       <c r="AV2" s="3" t="inlineStr"/>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX2" s="3" t="inlineStr"/>
@@ -4091,7 +4359,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>PZZA</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -4102,12 +4370,12 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG2" s="3" t="inlineStr">
@@ -4116,434 +4384,506 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T20:04:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>IBM 受七月營收不及預期影響，股價下跌，市場對其財務表現表現出擔憂。</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>PHM</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PulteGroup, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:22:46+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>普爾特集團因第三季財報未達預期，股價下跌，顯示市場對住宅需求的擔憂。</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>財報不如預期</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>PulteGroup</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNN1g2QmJPSjM4RGNlSFFkSmxheU0wQnp5UkVWSlpRU3drc05lMG1oQmZrRVZUbnlaaUNGVlBfd1ZSQ0V4YkhnYVh6dmNJVnZIUXRPek5VRlVfZDZocGNfTVRzZkNpMjhsWXhvNVdrNXo1UjRDbC1lZlVrRnM2TG03M280R3E3SWF0SzhBVHNPZGx6aVdzRnlRTEtYem9CT0hRWnREVDBPLVg3ZzgyRjBnc3B1OA?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>MarketWatch</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYm53VTh3QTFRckszZ25LR1dydXhWTlVXejhia2pMcjFkVl9XOFNteERCSmNLNGNXTDZ5aUwycjRaMWV3emdQYmtJdThObWVVNE9mNlBOQWxXcUZUdWdMQlBxYmtRWFFxa0lrZmpETkVPQ2tGUlh1dER2Rk5MR1AyR3ByVTlmajlpV1ItN3BVbDgyRjVxOFFORXdLT1VkUDVKRlp1VFEtd2NNZ0hTd0Vfdng2TTdkQ0ozUHZVcjY4SjYxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>4df070360f41de2f4d8ffca0</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>15814b5497b98f167c845463</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>c9b4b17dbf714cbcbbfcf5cb80d7eeab</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>121df6b8d1583e63199ddab7</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>a2ffa540ad4cc1c9e2785913</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> IBM’s stock falls as investors struggle to shake off July earnings miss &amp;nbsp;&amp;nbsp; MarketWatch </t>
-        </is>
-      </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand (PHM:NYSE) &amp;nbsp;&amp;nbsp; Seeking Alpha </t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>earnings miss</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>EARNINGS_MISS</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AK3" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_IMPLIED</t>
-        </is>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AM3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>PulteGroup stock dips as Q3 earnings miss estimates amid pressure on homebuying demand</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AQ3" s="4" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>PHM</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:32:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company Issues Fifth Profit Warning In Five Years</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>肯尼亞公司在五年內第五次發布利潤警告，顯示其財務表現不佳。</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T20:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>IBM 受七月營收不及預期影響，股價下跌，市場對其財務表現表現出擔憂。</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>財報不如預期</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUUJQQUVhaXJra3ZCVXVpdU5UT3JWU0lhOU5ETG9rbjJPM1RUbVBheE4teWZSRFJmRkU5N3dnWFlaZjdjSjJNSjAyTVhMcHZjUTdjSEZadmlnUkRvODd0TlJhVzFNYTRBX2Z2MnZXSFk2Sy1ZUDJoamg2SmpkVTFOMmRiVElPWThSb1ZEcG0tTGpMNDVQUS1j?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>The Kenya Times</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>a6d594bd8815899279a12f3d</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>ae9ecbb34a3046b47d87afd5</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNN1g2QmJPSjM4RGNlSFFkSmxheU0wQnp5UkVWSlpRU3drc05lMG1oQmZrRVZUbnlaaUNGVlBfd1ZSQ0V4YkhnYVh6dmNJVnZIUXRPek5VRlVfZDZocGNfTVRzZkNpMjhsWXhvNVdrNXo1UjRDbC1lZlVrRnM2TG03M280R3E3SWF0SzhBVHNPZGx6aVdzRnlRTEtYem9CT0hRWnREVDBPLVg3ZzgyRjBnc3B1OA?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>MarketWatch</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>625beff756514b18baea6459f9318ed9</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>4df070360f41de2f4d8ffca0</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>15814b5497b98f167c845463</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Kenyan Company Issues Fifth Profit Warning In Five Years &amp;nbsp;&amp;nbsp; The Kenya Times </t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> IBM’s stock falls as investors struggle to shake off July earnings miss &amp;nbsp;&amp;nbsp; MarketWatch </t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>profit warning</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AL4" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_IMPLIED</t>
+        </is>
+      </c>
+      <c r="AM4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
+        </is>
+      </c>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP4" s="4" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AQ4" s="4" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr"/>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr"/>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr"/>
-      <c r="BG4" s="3" t="inlineStr"/>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4556,40 +4896,44 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>RNDC</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22T04:14:22+08:00</t>
+          <t>2026-10-22T07:23:22+08:00</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
+          <t>Abbott to spin out Nutrition business, cuts guidance</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>RNDC 申請第 11 章破產，並計畫出售資產及逐步關閉營運。</t>
+          <t>阿博特公司將其營養業務拆分，並下調指引，屬於一般公司更新。</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>破產</t>
+          <t>財測下修</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -4613,51 +4957,51 @@
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>GENERAL_INFORMATION</t>
         </is>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>RNDC</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>公司代號待核對</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPaXkxbTd3WFRlMnNJQ1F0akZGS1BnYkR4bHBtODR6Ynhqb2hUWXVxNkdMVzNUUFJxNzJZMHdOR3MyQU5BMmptb3VDQ005ME40cHRRR3FkQXVtcTJkcl8yY3owRV9ZeWdCazBOVEh6SzVXX2lrOVRBMXQ5T09Qc3ljWldyUkVEZ1V5YkNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPVlY1aFVobmxHUG9RUGJ3UFdvSk44SzJNS3J6Ni1ZemEzTlY3LUFsdTVIc0ZCaENHX09VWUVIeThlMTQ4TkVYdUhyVUpHNmZfUXByR3BQSWk4YzRTTzRXS1BndGRGS2ZKS29Ebkoxb2tiZjlPZmx3cWFaaUd5QUJWRlIwTFVYdw?oc=5</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>National Association of Wholesaler-Distributors</t>
+          <t>MassDevice</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="inlineStr"/>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>EARNINGS_WARNING</t>
         </is>
       </c>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>26a18dcdf2284982ab66c202c8cc9615</t>
+          <t>7898337efd704d62ae39dbe64c320590</t>
         </is>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>fff03a0fd409bebaa971460f</t>
+          <t>9cd60119472fd0edfd22e915</t>
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>5a0e0d95455677066de7d303</t>
+          <t>8a85ef4535a887fa86a24eab</t>
         </is>
       </c>
       <c r="AE5" s="4" t="inlineStr"/>
@@ -4668,7 +5012,7 @@
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RNDC Files for Chapter 11, Pursues Sales and Wind-Down &amp;nbsp;&amp;nbsp; National Association of Wholesaler-Distributors </t>
+          <t xml:space="preserve"> Abbott to spin out Nutrition business, cuts guidance &amp;nbsp;&amp;nbsp; MassDevice </t>
         </is>
       </c>
       <c r="AH5" s="4" t="inlineStr">
@@ -4676,16 +5020,8 @@
           <t>en</t>
         </is>
       </c>
-      <c r="AI5" s="4" t="inlineStr">
-        <is>
-          <t>chapter 11</t>
-        </is>
-      </c>
-      <c r="AJ5" s="4" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
       <c r="AK5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4701,11 +5037,7 @@
           <t>False</t>
         </is>
       </c>
-      <c r="AN5" s="4" t="inlineStr">
-        <is>
-          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
-        </is>
-      </c>
+      <c r="AN5" s="4" t="inlineStr"/>
       <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
@@ -4723,34 +5055,58 @@
       </c>
       <c r="AR5" s="4" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AT5" s="4" t="inlineStr"/>
       <c r="AU5" s="4" t="inlineStr"/>
       <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="4" t="inlineStr"/>
       <c r="AZ5" s="4" t="inlineStr"/>
       <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
       <c r="BC5" s="4" t="inlineStr">
         <is>
-          <t>公司代號待核對</t>
+          <t>已核對</t>
         </is>
       </c>
       <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr"/>
-      <c r="BF5" s="4" t="inlineStr"/>
-      <c r="BG5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
       <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="4" t="inlineStr"/>
       <c r="BK5" s="4" t="inlineStr">
         <is>
@@ -4759,246 +5115,464 @@
       </c>
       <c r="BL5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26T15:43:17.016263+08:00</t>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RNDC</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:14:22+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>RNDC 申請第 11 章破產，並計畫出售資產及逐步關閉營運。</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>破產</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>RNDC</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>公司代號待核對</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPaXkxbTd3WFRlMnNJQ1F0akZGS1BnYkR4bHBtODR6Ynhqb2hUWXVxNkdMVzNUUFJxNzJZMHdOR3MyQU5BMmptb3VDQ005ME40cHRRR3FkQXVtcTJkcl8yY3owRV9ZeWdCazBOVEh6SzVXX2lrOVRBMXQ5T09Qc3ljWldyUkVEZ1V5YkNZ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>National Association of Wholesaler-Distributors</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>26a18dcdf2284982ab66c202c8cc9615</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>fff03a0fd409bebaa971460f</t>
+        </is>
+      </c>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>5a0e0d95455677066de7d303</t>
+        </is>
+      </c>
+      <c r="AE6" s="5" t="inlineStr"/>
+      <c r="AF6" s="5" t="inlineStr">
+        <is>
+          <t>MARKET_DISCOVERY</t>
+        </is>
+      </c>
+      <c r="AG6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RNDC Files for Chapter 11, Pursues Sales and Wind-Down &amp;nbsp;&amp;nbsp; National Association of Wholesaler-Distributors </t>
+        </is>
+      </c>
+      <c r="AH6" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="AI6" s="5" t="inlineStr">
+        <is>
+          <t>chapter 11</t>
+        </is>
+      </c>
+      <c r="AJ6" s="5" t="inlineStr">
+        <is>
+          <t>BANKRUPTCY</t>
+        </is>
+      </c>
+      <c r="AK6" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AL6" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AM6" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AN6" s="5" t="inlineStr">
+        <is>
+          <t>RNDC Files for Chapter 11, Pursues Sales and Wind-Down</t>
+        </is>
+      </c>
+      <c r="AO6" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP6" s="5" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AQ6" s="5" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AR6" s="5" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="AS6" s="5" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="AT6" s="5" t="inlineStr"/>
+      <c r="AU6" s="5" t="inlineStr"/>
+      <c r="AV6" s="5" t="inlineStr"/>
+      <c r="AW6" s="5" t="inlineStr"/>
+      <c r="AX6" s="5" t="inlineStr"/>
+      <c r="AY6" s="5" t="inlineStr"/>
+      <c r="AZ6" s="5" t="inlineStr"/>
+      <c r="BA6" s="5" t="inlineStr"/>
+      <c r="BB6" s="5" t="inlineStr"/>
+      <c r="BC6" s="5" t="inlineStr">
+        <is>
+          <t>公司代號待核對</t>
+        </is>
+      </c>
+      <c r="BD6" s="5" t="inlineStr"/>
+      <c r="BE6" s="5" t="inlineStr"/>
+      <c r="BF6" s="5" t="inlineStr"/>
+      <c r="BG6" s="5" t="inlineStr"/>
+      <c r="BH6" s="5" t="inlineStr"/>
+      <c r="BI6" s="5" t="inlineStr"/>
+      <c r="BJ6" s="5" t="inlineStr"/>
+      <c r="BK6" s="5" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>EONR</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>EON Resources Inc. Class A Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>2026-10-22T03:47:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Eon Resources 公司的 CEO 在面臨持續的營運疑慮警告時，表示公司仍具足夠流動性以維持營運。</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>繼續經營疑慮</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>GOING_CONCERN|LIQUIDITY_CRISIS</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Eon Resources</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNX0hvNGdTa0Vzakk2Sndrb0xlaFJzQWtVNzM5SHpTeWpjYUY2Y0FDdFljNkk5UllGakdhaWFSbXJfTTJTMmQzQl9Mc3ZhcGFyemphUmx0NFMyekcxVXlkX3Z2MXJXQldaRFpnT3JSNHhqc2Y5NThTM2NBTGdNMmVTNVRqREgyQVpxUEVON0FjdjNFS3k5UVhYdnN3?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Hart Energy</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>GOING_CONCERN</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>72f7e40ac43f43e3aff08819995be98f</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>b921d8e12af42c124b1a45c8</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>a18bd00bf42db9315918f062</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr"/>
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>MARKET_DISCOVERY</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"> Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings &amp;nbsp;&amp;nbsp; Hart Energy </t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr"/>
+      <c r="AJ7" s="5" t="inlineStr"/>
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="AL6" s="4" t="inlineStr">
+      <c r="AL7" s="5" t="inlineStr">
         <is>
           <t>RUMORED</t>
         </is>
       </c>
-      <c r="AM6" s="4" t="inlineStr">
+      <c r="AM7" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AN6" s="4" t="inlineStr">
+      <c r="AN7" s="5" t="inlineStr">
         <is>
           <t>Eon Resources CEO Defends Liquidity Despite Recurring Going-Concern Warnings</t>
         </is>
       </c>
-      <c r="AO6" s="4" t="inlineStr">
+      <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr">
+      <c r="AP7" s="5" t="inlineStr">
         <is>
           <t>openai/gpt-oss-20b</t>
         </is>
       </c>
-      <c r="AQ6" s="4" t="inlineStr">
+      <c r="AQ7" s="5" t="inlineStr">
         <is>
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AR6" s="4" t="inlineStr">
+      <c r="AR7" s="5" t="inlineStr">
         <is>
           <t>1465</t>
         </is>
       </c>
-      <c r="AS6" s="4" t="inlineStr">
+      <c r="AS7" s="5" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AT7" s="5" t="inlineStr"/>
+      <c r="AU7" s="5" t="inlineStr"/>
+      <c r="AV7" s="5" t="inlineStr"/>
+      <c r="AW7" s="5" t="inlineStr">
         <is>
           <t>NYSE American</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="5" t="inlineStr"/>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr">
         <is>
           <t>EONR</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC7" s="5" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG7" s="5" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr">
+      <c r="BH7" s="5" t="inlineStr"/>
+      <c r="BI7" s="5" t="inlineStr"/>
+      <c r="BJ7" s="5" t="inlineStr"/>
+      <c r="BK7" s="5" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL6" s="4" t="inlineStr">
+      <c r="BL7" s="5" t="inlineStr">
         <is>
           <t>2026-10-26T15:43:17.016263+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL6"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5009,7 +5583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5400,1746 +5974,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T23:26:14+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>US Stocks Fall Sharply as Philadelphia Semiconductor Index Drops Over 6%: What Caused the Decline?</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>無足夠資訊確認任何信用風險事件。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPX3N3OVFtWjJuWHRxSmVNU21oa0NqNUU4QktleWM5T3lsNE1Ra1Nna2xYVDM0eURqSmNLSktBcm1MNi0ySmI5NWw3T3pxNlFIbXhJa3RkczRxblo3WmJaS3dSQ2Z6d0JsWXVrX0cySzIzc1lmdHNFT1hPZkg5SXk3emtGNVl1LXhPVlY4Y1VsNlN2NVVnVi1iZThJUGRzMkFnV1lvT1ZxWDktZm5zTll5a3F0Y3VKN09QVWJydk1VTTBEYjg?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingKey</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>5a3dcc8b183e83f67a3ad671</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>ddef9ae56729e6c25c0a8e79</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> US Stocks Fall Sharply as Philadelphia Semiconductor Index Drops Over 6%: What Caused the Decline? &amp;nbsp;&amp;nbsp; TradingKey </t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="AS2" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr"/>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr"/>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T22:59:45+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>AI龍頭Meta帶領科技股下殺 美股週四開盤重挫、台積電暴跌逾4%</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Meta 相關訊息未顯示任何確定的違約或信用事件，僅提及市場股價波動，無法判斷是否存在信用風險升高或違約情形。</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wJBVV95cUxPWTdGUURmc2R1c1ZEbVh4d1ctWENyYTNJSUF1bzloSzJlRnc3VUM2VWRvTEdWckdZSkVCYy1fNWkzeWR2cjlGMjUtTlAtbnZadDd5b21OZWVMV0lZbFB4VThqZ1dyYnN1c0NZS0dTcGh2YlVoM3FNWEtzWUVaVXl1S204cUZ2YVJGc01JTUVsUDA4VmJPM3FjOU9sVW1WYUlYakJva1BmRzhEaXFzTmtwUlFoeWxYVmx6MENETWlJX1RJeWpzTjZPNmo0cTk5Sk13eEJfd19HSVBsd0hTMEdJSVkzTHU4WE9uYndNLUplazU3RWVSXzZjMFlWazdJWjRkUXp4RU9JVUJtVGtabmpMMUNBLUx5MDN1UXB0eGF5aFNOZEhvdW12TFdFWjZacnptR0dhM0dpeWRJOE5mS0FSd01WZEpFc2ZIR25jX2tiLS1xTjdsN2xHLXdpSjNTWkFWbTlUbndQZGh5YUNRbHdQeHdIVQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo新聞</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>804abe3a8136f62a9c1c950c</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>d618f5142a719fbe87afd83a</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> AI龍頭Meta帶領科技股下殺 美股週四開盤重挫、台積電暴跌逾4% &amp;nbsp;&amp;nbsp; Yahoo新聞 </t>
-        </is>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="inlineStr">
-        <is>
-          <t>重挫</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL3" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ3" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR3" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="AS3" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AT3" s="2" t="inlineStr">
-        <is>
-          <t>rate limited</t>
-        </is>
-      </c>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T22:51:47+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>美股異動 | 信用風險指標刷新紀錄 Meta(META.US)跌逾5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Meta 股價下跌逾5%，但未涉及任何違約或信用風險事件。</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>股價下跌</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPekhkbVN5QzZCeE9UVUg0WkQzTVdUU1lNdGF6RHhqaXBabVN4YkpnS1VlRXBoMmlRVVFDYlJ5VE1CalYwa2p2TzVNem5LQXBjdXN6S01KUlBLaENQbHNSY3VtdjNkS0loYkM2LTVMQW4yYkZneW5jTkw1QXJSYVdpb0h5WmI1U2U4NTRQcEpiVmZ1OVI1N3lna0dGRDUtUklubWtv?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>富途牛牛</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>c75869506577c88d3a17781a</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>7729522a85ed5ee0cb3121c9</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 美股異動 | 信用風險指標刷新紀錄 Meta(META.US)跌逾5% &amp;nbsp;&amp;nbsp; 富途牛牛 </t>
-        </is>
-      </c>
-      <c r="AH4" s="2" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL4" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_IMPLIED</t>
-        </is>
-      </c>
-      <c r="AM4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ4" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR4" s="2" t="inlineStr">
-        <is>
-          <t>1483</t>
-        </is>
-      </c>
-      <c r="AS4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T22:38:33+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>AI Infrastructure Debt Meets Rising Yields: Tech Stocks Face a Stress Test</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>無足夠資訊確認任何信用風險事件。</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPVDU3bmFjMDVYaGZCR0RDNVE0VExpNnhienZ4TERNMFVXbTVMZ3V3MDhST3dja05KaENjQjIwVXc0dlR1bnBybHMyVGk3dDh0dHVOYnFoN1B4d3QwZmZDb0cwWktUNFJMOFg0VTVFUzdvYTRtYmZCWXZNOXVidFYwVUtDMWtibXNRWmNzQjg2X1hxY0ZMSHowS1ZtWFRMUEJYSzN6Uw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gadget Review</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>50b863c0289f5cb1cca8cdd4</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>0bc95bf19d86e11cfffc7c11</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> AI Infrastructure Debt Meets Rising Yields: Tech Stocks Face a Stress Test &amp;nbsp;&amp;nbsp; Gadget Review </t>
-        </is>
-      </c>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>1461</t>
-        </is>
-      </c>
-      <c r="AS5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr"/>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr"/>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr"/>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>PZZA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Papa John's International, Inc.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T22:03:27+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>本新聞未提供足夠證據顯示 Papa John's International, Inc. 有任何違約、破產或其他信用風險事件，僅提及投資者可領導訴訟。</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>Papa John's International, Inc.</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxPM1I4Ujg5QzFMbVpvQWV0enFIVEtMVTdCd2N4eWp4ZUw1NXRRUkF4cDRsR0FHd0hhcnQzVnpXZTdnd2FYaW9FbV81SF9VNG51ZzJLRnVYNWY5azdtN0JlNXgybkpKaGViaW56MHhkd2R3YTc2ZV9DWlJ6YVdaOUhTOG1CNU5CNEJTM0I3WERiM0tDVFVXZFpkWnFFb3JXV3gzc250Q2hyVkFMb2NzVnJKQW5BMkFPeVVKLU1aaWpabFJ6YzV0UmdoclB6d0xSVHl6bEptN2EyQ29BV0FNaVl4RkljTHp4Z1EtanlORzBJd0c3V0Fvc1RQcEg4UGpQMEtLSW92ZGhQX0o0M2otbnRaMW5NeHZEb2dfeTZfOTNBVXhBazM1RE5rNmVVYk1ZMGw5c0pEaWVJekc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>The Daily Tribune News</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>9a99478b2900cd4f54743ca2</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>7f0886ef1cbe99fa784a57ba</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PZZA Investors Have Opportunity to Lead Papa John's International, Inc. Securities Fraud Lawsuit with SBS Law &amp;nbsp;&amp;nbsp; The Daily Tribune News </t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="AS6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>PZZA</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T20:04:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>IBM 受七月營收不及預期影響，股價下跌，市場對其財務表現表現出擔憂。</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS|PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNN1g2QmJPSjM4RGNlSFFkSmxheU0wQnp5UkVWSlpRU3drc05lMG1oQmZrRVZUbnlaaUNGVlBfd1ZSQ0V4YkhnYVh6dmNJVnZIUXRPek5VRlVfZDZocGNfTVRzZkNpMjhsWXhvNVdrNXo1UjRDbC1lZlVrRnM2TG03M280R3E3SWF0SzhBVHNPZGx6aVdzRnlRTEtYem9CT0hRWnREVDBPLVg3ZzgyRjBnc3B1OA?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>MarketWatch</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>4df070360f41de2f4d8ffca0</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>15814b5497b98f167c845463</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> IBM’s stock falls as investors struggle to shake off July earnings miss &amp;nbsp;&amp;nbsp; MarketWatch </t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI7" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AJ7" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_IMPLIED</t>
-        </is>
-      </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s stock falls as investors struggle to shake off July earnings miss</t>
-        </is>
-      </c>
-      <c r="AO7" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ7" s="3" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>1459</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T16:32:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company Issues Fifth Profit Warning In Five Years</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>肯尼亞公司在五年內第五次發布利潤警告，顯示其財務表現不佳。</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>財測下修</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>Kenyan Company</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQUUJQQUVhaXJra3ZCVXVpdU5UT3JWU0lhOU5ETG9rbjJPM1RUbVBheE4teWZSRFJmRkU5N3dnWFlaZjdjSjJNSjAyTVhMcHZjUTdjSEZadmlnUkRvODd0TlJhVzFNYTRBX2Z2MnZXSFk2Sy1ZUDJoamg2SmpkVTFOMmRiVElPWThSb1ZEcG0tTGpMNDVQUS1j?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>The Kenya Times</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>a6d594bd8815899279a12f3d</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>ae9ecbb34a3046b47d87afd5</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Kenyan Company Issues Fifth Profit Warning In Five Years &amp;nbsp;&amp;nbsp; The Kenya Times </t>
-        </is>
-      </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI8" s="3" t="inlineStr">
-        <is>
-          <t>profit warning</t>
-        </is>
-      </c>
-      <c r="AJ8" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_WARNING</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr"/>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>公司代號待核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T12:24:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>《港股》美股下挫、陸股墜熊市 恆指暴跌近3% AI、晶片股遭血洗</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>無可辨識的信用風險事件。</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNcWVSd2VKR3ZETnd3dHhPaE1QM2JJakNFN2ltTHhlQ1NaQU9jSW5BSUdiNl9IWXg0eDFHUkZRYnBHTDVaanE5aVRlSFlmQm9iN3NwRTFzRUJNYUZPMzg4OE0xbnY4Q3RFcWlNVzY1QmRaNGtiTVBrV0Qwdm85TGphakxTNjhwU09f?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>富聯網</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>fbff431e27558bb00d62e9a4</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>9f593009b155d86c74bfb363</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 《港股》美股下挫、陸股墜熊市 恆指暴跌近3% AI、晶片股遭血洗 &amp;nbsp;&amp;nbsp; 富聯網 </t>
-        </is>
-      </c>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL9" s="2" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AM9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ9" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR9" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="AS9" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr"/>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr"/>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>市場／多公司或主體待辨識</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr"/>
-      <c r="BE9" s="2" t="inlineStr"/>
-      <c r="BF9" s="2" t="inlineStr"/>
-      <c r="BG9" s="2" t="inlineStr"/>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T07:23:22+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Abbott to spin out Nutrition business, cuts guidance</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>阿博特公司將其營養業務拆分，並下調指引，屬於一般公司更新。</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>一般公司更新</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>排除、不納入風險事件</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL_INFORMATION</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPVlY1aFVobmxHUG9RUGJ3UFdvSk44SzJNS3J6Ni1ZemEzTlY3LUFsdTVIc0ZCaENHX09VWUVIeThlMTQ4TkVYdUhyVUpHNmZfUXByR3BQSWk4YzRTTzRXS1BndGRGS2ZKS29Ebkoxb2tiZjlPZmx3cWFaaUd5QUJWRlIwTFVYdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>MassDevice</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>GENERAL_INFORMATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>9cd60119472fd0edfd22e915</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>8a85ef4535a887fa86a24eab</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr">
-        <is>
-          <t>MARKET_DISCOVERY</t>
-        </is>
-      </c>
-      <c r="AG10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Abbott to spin out Nutrition business, cuts guidance &amp;nbsp;&amp;nbsp; MassDevice </t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="AM10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP10" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AQ10" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AR10" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="AS10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL10"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-22.xlsx
+++ b/news_daily/2026-10-22.xlsx
@@ -3147,17 +3147,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>已分類</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
@@ -3198,7 +3198,11 @@
       </c>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>1c1f352ea3664f1888f3b77a8c0572cc</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>93fbb9f14d67c9fca1f296d6</t>
@@ -3313,8 +3317,16 @@
       <c r="BH12" s="2" t="inlineStr"/>
       <c r="BI12" s="2" t="inlineStr"/>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
